--- a/data/trans_bre/P16A04-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P16A04-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 0,53</t>
+          <t>-2,85; 0,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 2,51</t>
+          <t>-2,74; 2,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 0,37</t>
+          <t>-4,1; 0,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,83; 4,92</t>
+          <t>0,7; 4,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-90,57; 67,51</t>
+          <t>-89,47; 127,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-72,63; 168,3</t>
+          <t>-70,88; 188,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-89,95; 47,48</t>
+          <t>-90,8; 46,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>22,3; 526,55</t>
+          <t>26,96; 566,51</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 3,77</t>
+          <t>-0,18; 3,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 2,24</t>
+          <t>-1,74; 2,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 1,37</t>
+          <t>-2,43; 1,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 1,83</t>
+          <t>-1,54; 1,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-34,99; 1037,3</t>
+          <t>-22,99; 1226,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-67,89; 221,41</t>
+          <t>-62,9; 215,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-90,12; 205,04</t>
+          <t>-87,36; 199,3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-63,59; 234,47</t>
+          <t>-68,62; 171,74</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 5,47</t>
+          <t>-0,47; 5,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 1,91</t>
+          <t>-3,34; 2,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 8,53</t>
+          <t>0,35; 8,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 6,45</t>
+          <t>-1,41; 6,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-35,32; 671,59</t>
+          <t>-34,01; 543,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-74,88; 78,57</t>
+          <t>-71,37; 83,81</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-10,99; 1229,02</t>
+          <t>-11,16; 1244,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-35,13; 464,9</t>
+          <t>-27,59; 535,21</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 2,58</t>
+          <t>-0,36; 2,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 3,31</t>
+          <t>-0,27; 3,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 2,5</t>
+          <t>-0,46; 2,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 1,52</t>
+          <t>-1,45; 1,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-15,62; 183,3</t>
+          <t>-16,84; 197,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-10,19; 144,37</t>
+          <t>-9,09; 155,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-14,77; 137,77</t>
+          <t>-15,9; 151,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-49,83; 103,43</t>
+          <t>-52,52; 91,96</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 1,29</t>
+          <t>-3,3; 1,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 0,64</t>
+          <t>-3,11; 0,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 1,91</t>
+          <t>-1,5; 1,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,27; 4,39</t>
+          <t>0,29; 4,72</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-71,88; 79,66</t>
+          <t>-68,34; 80,93</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-70,51; 29,84</t>
+          <t>-68,29; 36,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-49,47; 165,8</t>
+          <t>-48,32; 156,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,77; 350,99</t>
+          <t>1,17; 382,69</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 2,12</t>
+          <t>-0,28; 2,1</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 2,84</t>
+          <t>-0,45; 2,87</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 1,85</t>
+          <t>-1,15; 1,79</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-7,85; 1,57</t>
+          <t>-6,58; 1,45</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-37,37; —</t>
+          <t>-32,23; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-32,34; —</t>
+          <t>-38,84; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-56,26; 527,56</t>
+          <t>-55,35; 532,21</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-81,28; 164,66</t>
+          <t>-78,3; 119,54</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 1,04</t>
+          <t>-0,26; 1,12</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 0,8</t>
+          <t>-0,82; 0,84</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 0,89</t>
+          <t>-0,51; 0,98</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 1,65</t>
+          <t>-0,19; 1,68</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-14,6; 68,47</t>
+          <t>-12,95; 76,08</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-26,24; 34,47</t>
+          <t>-25,46; 34,91</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-22,36; 50,69</t>
+          <t>-21,45; 53,73</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 93,6</t>
+          <t>-7,34; 93,73</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A04-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P16A04-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,65</t>
+          <t>2,58</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>180,84%</t>
+          <t>175,28%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 0,76</t>
+          <t>-2,83; 0,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 2,39</t>
+          <t>-2,53; 2,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 0,36</t>
+          <t>-4,17; 0,46</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,7; 4,56</t>
+          <t>0,77; 4,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-89,47; 127,84</t>
+          <t>-90,15; 119,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-70,88; 188,39</t>
+          <t>-69,66; 192,88</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-90,8; 46,34</t>
+          <t>-91,01; 45,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>26,96; 566,51</t>
+          <t>23,17; 568,96</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,08</t>
+          <t>0,01</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>0,49%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 3,72</t>
+          <t>-0,13; 3,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 2,11</t>
+          <t>-1,79; 2,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 1,23</t>
+          <t>-2,63; 1,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 1,59</t>
+          <t>-1,38; 1,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-22,99; 1226,68</t>
+          <t>-26,9; 946,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-62,9; 215,34</t>
+          <t>-67,6; 252,24</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-87,36; 199,3</t>
+          <t>-87,37; 139,06</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-68,62; 171,74</t>
+          <t>-62,78; 191,9</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,76</t>
+          <t>0,49</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>56,22%</t>
+          <t>10,91%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 5,78</t>
+          <t>-0,54; 6,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 2,05</t>
+          <t>-3,19; 2,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,35; 8,32</t>
+          <t>0,56; 8,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 6,8</t>
+          <t>-2,73; 4,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-34,01; 543,82</t>
+          <t>-36,48; 521,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-71,37; 83,81</t>
+          <t>-67,84; 89,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-11,16; 1244,64</t>
+          <t>-15,15; 1175,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-27,59; 535,21</t>
+          <t>-46,99; 142,55</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,16</t>
+          <t>0,66</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>28,4%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 2,62</t>
+          <t>-0,32; 2,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 3,58</t>
+          <t>-0,38; 3,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 2,63</t>
+          <t>-0,53; 2,65</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 1,42</t>
+          <t>-0,86; 1,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-16,84; 197,87</t>
+          <t>-15,59; 190,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-9,09; 155,06</t>
+          <t>-13,62; 150,7</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-15,9; 151,23</t>
+          <t>-19,99; 153,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-52,52; 91,96</t>
+          <t>-28,63; 118,66</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,12</t>
+          <t>2,44</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>111,09%</t>
+          <t>141,29%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 1,36</t>
+          <t>-2,89; 1,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 0,68</t>
+          <t>-3,12; 0,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 1,94</t>
+          <t>-1,38; 1,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,29; 4,72</t>
+          <t>0,92; 4,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-68,34; 80,93</t>
+          <t>-66,28; 97,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-68,29; 36,49</t>
+          <t>-70,93; 28,53</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-48,32; 156,53</t>
+          <t>-47,8; 155,48</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,17; 382,69</t>
+          <t>33,24; 420,14</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-1,2</t>
+          <t>-0,77</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-33,43%</t>
+          <t>-22,59%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 2,1</t>
+          <t>-0,45; 2,13</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 2,87</t>
+          <t>-0,23; 3,02</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 1,79</t>
+          <t>-1,32; 1,73</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 1,45</t>
+          <t>-6,16; 1,79</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-32,23; —</t>
+          <t>-38,21; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-38,84; —</t>
+          <t>-31,03; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-55,35; 532,21</t>
+          <t>-57,94; 535,67</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-78,3; 119,54</t>
+          <t>-75,71; 153,13</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,78</t>
+          <t>0,9</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>38,27%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 1,12</t>
+          <t>-0,33; 1,13</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 0,84</t>
+          <t>-0,86; 0,84</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 0,98</t>
+          <t>-0,55; 0,97</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 1,68</t>
+          <t>0,03; 1,62</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-12,95; 76,08</t>
+          <t>-15,69; 73,79</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-25,46; 34,91</t>
+          <t>-25,8; 35,59</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-21,45; 53,73</t>
+          <t>-22,32; 57,77</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-7,34; 93,73</t>
+          <t>-0,05; 85,02</t>
         </is>
       </c>
     </row>
